--- a/Deliverables/SM_Top Board/_BOM/CLient_BOM_Top_Board.xlsx
+++ b/Deliverables/SM_Top Board/_BOM/CLient_BOM_Top_Board.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ColeBenson-SmartMotors\Deliverables\SM_Top Board\_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6222EFBB-2B39-40C7-B789-AE46BB6E87BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="396">
   <si>
     <t>Component list</t>
   </si>
@@ -53,12 +52,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>SM_Top_Board.PrjPcb</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Designator</t>
   </si>
   <si>
@@ -1208,12 +1201,6 @@
     <t>IC</t>
   </si>
   <si>
-    <t>Bill of Materials for Project (Smartmotors)</t>
-  </si>
-  <si>
-    <t>(Smartmotors)</t>
-  </si>
-  <si>
     <t>CRH2512FR033E04Z</t>
   </si>
   <si>
@@ -1221,12 +1208,21 @@
   </si>
   <si>
     <t>RTT03R330FTP</t>
+  </si>
+  <si>
+    <t>Top_Board</t>
+  </si>
+  <si>
+    <t>Smart Motors</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project (Smart Motors)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -1785,15 +1781,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1805,6 +1792,15 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1849,7 +1845,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2145,7 +2141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2171,9 +2167,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2184,7 +2180,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="54" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2201,13 +2197,13 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="55" t="s">
-        <v>7</v>
+        <v>393</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="59"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2218,13 +2214,13 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="56" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="60"/>
+      <c r="K4" s="64"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2234,14 +2230,12 @@
         <v>3</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="57" t="s">
-        <v>8</v>
-      </c>
+      <c r="F5" s="57"/>
       <c r="G5" s="14"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="60"/>
+      <c r="K5" s="64"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2254,7 +2248,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
-      <c r="K6" s="60"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2267,7 +2261,7 @@
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="60"/>
+      <c r="K7" s="64"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2280,7 +2274,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-      <c r="K8" s="60"/>
+      <c r="K8" s="64"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2288,31 +2282,31 @@
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2321,26 +2315,26 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="62" t="s">
-        <v>379</v>
+      <c r="C10" s="59" t="s">
+        <v>377</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J10" s="37">
         <v>1</v>
@@ -2353,26 +2347,26 @@
         <f t="shared" ref="B11:B93" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="63" t="s">
-        <v>379</v>
+      <c r="C11" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J11" s="39">
         <v>9</v>
@@ -2385,26 +2379,26 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="64" t="s">
-        <v>379</v>
+      <c r="C12" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J12" s="37">
         <v>1</v>
@@ -2417,26 +2411,26 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
-        <v>379</v>
+      <c r="C13" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J13" s="39">
         <v>2</v>
@@ -2449,26 +2443,26 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="64" t="s">
-        <v>379</v>
+      <c r="C14" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J14" s="37">
         <v>9</v>
@@ -2481,26 +2475,26 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="63" t="s">
-        <v>379</v>
+      <c r="C15" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I15" s="40" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J15" s="39">
         <v>1</v>
@@ -2513,26 +2507,26 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="64" t="s">
-        <v>379</v>
+      <c r="C16" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I16" s="38" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J16" s="37">
         <v>4</v>
@@ -2545,26 +2539,26 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="63" t="s">
-        <v>379</v>
+      <c r="C17" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I17" s="40" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J17" s="39">
         <v>1</v>
@@ -2577,26 +2571,26 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="64" t="s">
-        <v>379</v>
+      <c r="C18" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I18" s="38" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J18" s="37">
         <v>3</v>
@@ -2609,26 +2603,26 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="63" t="s">
-        <v>379</v>
+      <c r="C19" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I19" s="40" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J19" s="39">
         <v>4</v>
@@ -2641,26 +2635,26 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="64" t="s">
-        <v>379</v>
+      <c r="C20" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J20" s="37">
         <v>1</v>
@@ -2673,26 +2667,26 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="63" t="s">
-        <v>379</v>
+      <c r="C21" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I21" s="40" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J21" s="39">
         <v>1</v>
@@ -2705,26 +2699,26 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="64" t="s">
-        <v>379</v>
+      <c r="C22" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J22" s="37">
         <v>2</v>
@@ -2737,26 +2731,26 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="63" t="s">
-        <v>379</v>
+      <c r="C23" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G23" s="40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I23" s="40" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J23" s="39">
         <v>4</v>
@@ -2769,26 +2763,26 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="64" t="s">
-        <v>379</v>
+      <c r="C24" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I24" s="38" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J24" s="37">
         <v>1</v>
@@ -2801,26 +2795,26 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="63" t="s">
-        <v>379</v>
+      <c r="C25" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G25" s="40" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H25" s="39" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I25" s="40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J25" s="39">
         <v>3</v>
@@ -2833,26 +2827,26 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="64" t="s">
-        <v>379</v>
+      <c r="C26" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G26" s="38">
         <v>885012205080</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I26" s="38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J26" s="37">
         <v>1</v>
@@ -2865,26 +2859,26 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="63" t="s">
-        <v>379</v>
+      <c r="C27" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D27" s="39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G27" s="40" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H27" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I27" s="40" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J27" s="39">
         <v>1</v>
@@ -2897,26 +2891,26 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="64" t="s">
-        <v>379</v>
+      <c r="C28" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I28" s="38" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J28" s="37">
         <v>1</v>
@@ -2929,26 +2923,26 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="63" t="s">
-        <v>379</v>
+      <c r="C29" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G29" s="40" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H29" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I29" s="40" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J29" s="39">
         <v>1</v>
@@ -2961,26 +2955,26 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="64" t="s">
-        <v>379</v>
+      <c r="C30" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I30" s="38" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J30" s="37">
         <v>3</v>
@@ -2993,26 +2987,26 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="63" t="s">
-        <v>379</v>
+      <c r="C31" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F31" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H31" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I31" s="40" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J31" s="39">
         <v>1</v>
@@ -3025,26 +3019,26 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="64" t="s">
-        <v>379</v>
+      <c r="C32" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I32" s="38" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J32" s="37">
         <v>1</v>
@@ -3057,26 +3051,26 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="63" t="s">
-        <v>379</v>
+      <c r="C33" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F33" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H33" s="39" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J33" s="39">
         <v>1</v>
@@ -3089,26 +3083,26 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="64" t="s">
-        <v>379</v>
+      <c r="C34" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I34" s="38" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J34" s="37">
         <v>1</v>
@@ -3121,26 +3115,26 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="63" t="s">
-        <v>379</v>
+      <c r="C35" s="60" t="s">
+        <v>377</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G35" s="40" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I35" s="40" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J35" s="39">
         <v>1</v>
@@ -3153,26 +3147,26 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="64" t="s">
-        <v>379</v>
+      <c r="C36" s="61" t="s">
+        <v>377</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I36" s="38" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J36" s="37">
         <v>4</v>
@@ -3185,26 +3179,26 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="63" t="s">
-        <v>380</v>
+      <c r="C37" s="60" t="s">
+        <v>378</v>
       </c>
       <c r="D37" s="39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F37" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G37" s="40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H37" s="39" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I37" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J37" s="39">
         <v>1</v>
@@ -3217,26 +3211,26 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="64" t="s">
-        <v>380</v>
+      <c r="C38" s="61" t="s">
+        <v>378</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I38" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J38" s="37">
         <v>1</v>
@@ -3249,26 +3243,26 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="63" t="s">
-        <v>380</v>
+      <c r="C39" s="60" t="s">
+        <v>378</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F39" s="39" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G39" s="40" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I39" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J39" s="39">
         <v>1</v>
@@ -3281,26 +3275,26 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="64" t="s">
-        <v>380</v>
+      <c r="C40" s="61" t="s">
+        <v>378</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I40" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J40" s="37">
         <v>8</v>
@@ -3313,26 +3307,26 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="63" t="s">
-        <v>382</v>
+      <c r="C41" s="60" t="s">
+        <v>380</v>
       </c>
       <c r="D41" s="39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F41" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H41" s="39" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J41" s="39">
         <v>1</v>
@@ -3345,26 +3339,26 @@
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="64" t="s">
-        <v>381</v>
+      <c r="C42" s="61" t="s">
+        <v>379</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I42" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J42" s="37">
         <v>4</v>
@@ -3377,26 +3371,26 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="63" t="s">
-        <v>383</v>
+      <c r="C43" s="60" t="s">
+        <v>381</v>
       </c>
       <c r="D43" s="39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F43" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G43" s="40" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H43" s="39" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I43" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J43" s="39">
         <v>1</v>
@@ -3409,26 +3403,26 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="64" t="s">
-        <v>383</v>
+      <c r="C44" s="61" t="s">
+        <v>381</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G44" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I44" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J44" s="37">
         <v>2</v>
@@ -3441,26 +3435,26 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="63" t="s">
-        <v>384</v>
+      <c r="C45" s="60" t="s">
+        <v>382</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G45" s="40" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H45" s="39" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I45" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J45" s="39">
         <v>1</v>
@@ -3473,26 +3467,26 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="64" t="s">
-        <v>384</v>
+      <c r="C46" s="61" t="s">
+        <v>382</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J46" s="37">
         <v>1</v>
@@ -3505,26 +3499,26 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="63" t="s">
-        <v>381</v>
+      <c r="C47" s="60" t="s">
+        <v>379</v>
       </c>
       <c r="D47" s="39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F47" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G47" s="40" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H47" s="39" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I47" s="40" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J47" s="39">
         <v>1</v>
@@ -3537,26 +3531,26 @@
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="64" t="s">
-        <v>381</v>
+      <c r="C48" s="61" t="s">
+        <v>379</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G48" s="38" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J48" s="37">
         <v>1</v>
@@ -3569,26 +3563,26 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="63" t="s">
-        <v>385</v>
+      <c r="C49" s="60" t="s">
+        <v>383</v>
       </c>
       <c r="D49" s="39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F49" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G49" s="40" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H49" s="39" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I49" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J49" s="39">
         <v>1</v>
@@ -3601,26 +3595,26 @@
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="64" t="s">
-        <v>385</v>
+      <c r="C50" s="61" t="s">
+        <v>383</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J50" s="37">
         <v>1</v>
@@ -3633,26 +3627,26 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="63" t="s">
-        <v>383</v>
+      <c r="C51" s="60" t="s">
+        <v>381</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F51" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G51" s="40" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H51" s="39" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I51" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J51" s="39">
         <v>2</v>
@@ -3665,26 +3659,26 @@
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="64" t="s">
-        <v>343</v>
+      <c r="C52" s="61" t="s">
+        <v>341</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G52" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J52" s="37">
         <v>4</v>
@@ -3697,26 +3691,26 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="63" t="s">
-        <v>384</v>
+      <c r="C53" s="60" t="s">
+        <v>382</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F53" s="39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G53" s="40">
         <v>61300211121</v>
       </c>
       <c r="H53" s="39" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I53" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J53" s="39">
         <v>4</v>
@@ -3729,26 +3723,26 @@
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="64" t="s">
-        <v>386</v>
+      <c r="C54" s="61" t="s">
+        <v>384</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E54" s="38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G54" s="38" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I54" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J54" s="37">
         <v>8</v>
@@ -3761,26 +3755,26 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="63" t="s">
-        <v>387</v>
+      <c r="C55" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F55" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G55" s="40" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H55" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I55" s="40" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J55" s="39">
         <v>2</v>
@@ -3793,26 +3787,26 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="64" t="s">
-        <v>387</v>
+      <c r="C56" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E56" s="38" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G56" s="38" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I56" s="38" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J56" s="37">
         <v>1</v>
@@ -3825,26 +3819,26 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="63" t="s">
-        <v>387</v>
+      <c r="C57" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D57" s="39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F57" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H57" s="39" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I57" s="40" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J57" s="39">
         <v>1</v>
@@ -3857,26 +3851,26 @@
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
-      <c r="C58" s="64" t="s">
-        <v>387</v>
+      <c r="C58" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G58" s="38" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I58" s="38" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J58" s="37">
         <v>2</v>
@@ -3889,26 +3883,26 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="63" t="s">
-        <v>387</v>
+      <c r="C59" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D59" s="39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F59" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H59" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I59" s="40" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J59" s="39">
         <v>4</v>
@@ -3921,26 +3915,26 @@
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="64" t="s">
-        <v>387</v>
+      <c r="C60" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I60" s="38" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J60" s="37">
         <v>4</v>
@@ -3953,26 +3947,26 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="63" t="s">
-        <v>387</v>
+      <c r="C61" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D61" s="39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F61" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G61" s="40" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H61" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I61" s="40" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J61" s="39">
         <v>8</v>
@@ -3985,26 +3979,26 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="64" t="s">
-        <v>387</v>
+      <c r="C62" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D62" s="37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E62" s="38" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G62" s="38" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I62" s="38" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J62" s="37">
         <v>1</v>
@@ -4017,26 +4011,26 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="63" t="s">
-        <v>387</v>
+      <c r="C63" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F63" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G63" s="40" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H63" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I63" s="40" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J63" s="39">
         <v>1</v>
@@ -4049,26 +4043,26 @@
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
-      <c r="C64" s="64" t="s">
-        <v>387</v>
+      <c r="C64" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I64" s="38" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J64" s="37">
         <v>1</v>
@@ -4081,26 +4075,26 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="63" t="s">
-        <v>387</v>
+      <c r="C65" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F65" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G65" s="40" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H65" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I65" s="40" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J65" s="39">
         <v>1</v>
@@ -4113,26 +4107,26 @@
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="64" t="s">
-        <v>387</v>
+      <c r="C66" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I66" s="38" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J66" s="37">
         <v>1</v>
@@ -4145,26 +4139,26 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="63" t="s">
-        <v>387</v>
+      <c r="C67" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F67" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G67" s="40" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I67" s="40" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J67" s="39">
         <v>1</v>
@@ -4177,26 +4171,26 @@
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="64" t="s">
-        <v>387</v>
+      <c r="C68" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I68" s="38" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J68" s="37">
         <v>1</v>
@@ -4209,26 +4203,26 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="63" t="s">
-        <v>387</v>
+      <c r="C69" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D69" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E69" s="40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F69" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G69" s="40" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H69" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I69" s="40" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J69" s="39">
         <v>1</v>
@@ -4241,26 +4235,26 @@
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="64" t="s">
-        <v>387</v>
+      <c r="C70" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I70" s="38" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J70" s="37">
         <v>1</v>
@@ -4273,26 +4267,26 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="63" t="s">
-        <v>387</v>
+      <c r="C71" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F71" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G71" s="40" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H71" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I71" s="40" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J71" s="39">
         <v>1</v>
@@ -4305,26 +4299,26 @@
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="64" t="s">
-        <v>387</v>
+      <c r="C72" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I72" s="38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J72" s="37">
         <v>2</v>
@@ -4337,26 +4331,26 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="63" t="s">
-        <v>387</v>
+      <c r="C73" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D73" s="39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F73" s="39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H73" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I73" s="40" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J73" s="39">
         <v>1</v>
@@ -4369,26 +4363,26 @@
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="64" t="s">
-        <v>387</v>
+      <c r="C74" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E74" s="38" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H74" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I74" s="38" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J74" s="37">
         <v>2</v>
@@ -4401,26 +4395,26 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="63" t="s">
-        <v>387</v>
+      <c r="C75" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D75" s="39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F75" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G75" s="40" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H75" s="39" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I75" s="40" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J75" s="39">
         <v>1</v>
@@ -4433,26 +4427,26 @@
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="64" t="s">
-        <v>387</v>
+      <c r="C76" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H76" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I76" s="38" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J76" s="37">
         <v>1</v>
@@ -4465,26 +4459,26 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="63" t="s">
-        <v>387</v>
+      <c r="C77" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F77" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G77" s="40" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I77" s="40" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J77" s="39">
         <v>1</v>
@@ -4497,26 +4491,26 @@
         <f>ROW(B78) - ROW($B$9)</f>
         <v>69</v>
       </c>
-      <c r="C78" s="64" t="s">
-        <v>387</v>
+      <c r="C78" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E78" s="38" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="H78" s="37" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I78" s="38" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J78" s="37">
         <v>1</v>
@@ -4529,26 +4523,26 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="63" t="s">
-        <v>387</v>
+      <c r="C79" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D79" s="39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F79" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G79" s="40" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I79" s="40" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J79" s="39">
         <v>1</v>
@@ -4561,26 +4555,26 @@
         <f>ROW(B80) - ROW($B$9)</f>
         <v>71</v>
       </c>
-      <c r="C80" s="64" t="s">
-        <v>387</v>
+      <c r="C80" s="61" t="s">
+        <v>385</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E80" s="38" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G80" s="38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H80" s="37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I80" s="38" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J80" s="37">
         <v>4</v>
@@ -4593,26 +4587,26 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="63" t="s">
-        <v>387</v>
+      <c r="C81" s="60" t="s">
+        <v>385</v>
       </c>
       <c r="D81" s="39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F81" s="39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G81" s="40" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H81" s="39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I81" s="40" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J81" s="39">
         <v>4</v>
@@ -4625,26 +4619,26 @@
         <f>ROW(B82) - ROW($B$9)</f>
         <v>73</v>
       </c>
-      <c r="C82" s="64" t="s">
-        <v>212</v>
+      <c r="C82" s="61" t="s">
+        <v>210</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E82" s="38" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F82" s="37" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G82" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H82" s="37" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="I82" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J82" s="37">
         <v>11</v>
@@ -4657,24 +4651,24 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="63" t="s">
-        <v>389</v>
+      <c r="C83" s="60" t="s">
+        <v>387</v>
       </c>
       <c r="D83" s="39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E83" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F83" s="39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G83" s="40"/>
       <c r="H83" s="39" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I83" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J83" s="39">
         <v>1</v>
@@ -4687,26 +4681,26 @@
         <f>ROW(B84) - ROW($B$9)</f>
         <v>75</v>
       </c>
-      <c r="C84" s="64" t="s">
-        <v>390</v>
+      <c r="C84" s="61" t="s">
+        <v>388</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E84" s="38" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G84" s="38">
         <v>750314597</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I84" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J84" s="37">
         <v>1</v>
@@ -4719,24 +4713,24 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="63" t="s">
-        <v>391</v>
+      <c r="C85" s="60" t="s">
+        <v>389</v>
       </c>
       <c r="D85" s="39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F85" s="39"/>
       <c r="G85" s="40" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H85" s="39" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I85" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J85" s="39">
         <v>1</v>
@@ -4749,26 +4743,26 @@
         <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="64" t="s">
-        <v>391</v>
+      <c r="C86" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I86" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J86" s="37">
         <v>1</v>
@@ -4781,26 +4775,26 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="63" t="s">
-        <v>391</v>
+      <c r="C87" s="60" t="s">
+        <v>389</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E87" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F87" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G87" s="40" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H87" s="39" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I87" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J87" s="39">
         <v>1</v>
@@ -4813,26 +4807,26 @@
         <f>ROW(B88) - ROW($B$9)</f>
         <v>79</v>
       </c>
-      <c r="C88" s="64" t="s">
-        <v>391</v>
+      <c r="C88" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E88" s="38" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G88" s="38" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I88" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J88" s="37">
         <v>1</v>
@@ -4845,26 +4839,26 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="C89" s="63" t="s">
-        <v>391</v>
+      <c r="C89" s="60" t="s">
+        <v>389</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G89" s="40" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H89" s="39" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I89" s="40" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J89" s="39">
         <v>1</v>
@@ -4877,26 +4871,26 @@
         <f>ROW(B90) - ROW($B$9)</f>
         <v>81</v>
       </c>
-      <c r="C90" s="64" t="s">
-        <v>391</v>
+      <c r="C90" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="D90" s="37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E90" s="38" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G90" s="38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H90" s="37" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I90" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J90" s="37">
         <v>1</v>
@@ -4909,26 +4903,26 @@
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="C91" s="63" t="s">
-        <v>391</v>
+      <c r="C91" s="60" t="s">
+        <v>389</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F91" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G91" s="40" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H91" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="I91" s="61" t="s">
-        <v>377</v>
+        <v>313</v>
+      </c>
+      <c r="I91" s="58" t="s">
+        <v>375</v>
       </c>
       <c r="J91" s="39">
         <v>1</v>
@@ -4941,26 +4935,26 @@
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="64" t="s">
-        <v>391</v>
+      <c r="C92" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="D92" s="37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E92" s="38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G92" s="38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I92" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J92" s="37">
         <v>1</v>
@@ -4973,26 +4967,26 @@
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="C93" s="63" t="s">
-        <v>391</v>
+      <c r="C93" s="60" t="s">
+        <v>389</v>
       </c>
       <c r="D93" s="39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F93" s="39" t="s">
+        <v>372</v>
+      </c>
+      <c r="G93" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="H93" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="I93" s="40" t="s">
         <v>374</v>
-      </c>
-      <c r="G93" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="H93" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="I93" s="40" t="s">
-        <v>376</v>
       </c>
       <c r="J93" s="39">
         <v>1</v>
@@ -5005,26 +4999,26 @@
         <f>ROW(B94) - ROW($B$9)</f>
         <v>85</v>
       </c>
-      <c r="C94" s="64" t="s">
-        <v>391</v>
+      <c r="C94" s="61" t="s">
+        <v>389</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F94" s="37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G94" s="38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H94" s="37" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I94" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J94" s="37">
         <v>1</v>
